--- a/output/pdf_financials_xlsx/HERB.xlsx
+++ b/output/pdf_financials_xlsx/HERB.xlsx
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.222392</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.274786</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.197138</v>
       </c>
     </row>
     <row r="35">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.222392</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.274786</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.197138</v>
       </c>
     </row>
     <row r="37">
@@ -1188,13 +1188,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.361523</v>
+        <v>0.139131</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.475421</v>
+        <v>0.200635</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.755362</v>
+        <v>0.5582240000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">

--- a/output/pdf_financials_xlsx/HERB.xlsx
+++ b/output/pdf_financials_xlsx/HERB.xlsx
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.03736</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.005633</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.0336</v>
       </c>
     </row>
     <row r="111">
@@ -3682,7 +3682,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>0.03736</v>
       </c>
